--- a/Kейс1_РазнесениеВыписки1С/resource/statement.xlsx
+++ b/Kейс1_РазнесениеВыписки1С/resource/statement.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C3BF823-4692-4F09-9711-ADC99E139B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3710C60-3EBF-4CCE-9BFB-C48B110061F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2194" yWindow="2194" windowWidth="24686" windowHeight="13166" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19260" yWindow="3885" windowWidth="15960" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="58">
   <si>
     <t>Дата</t>
   </si>
@@ -125,9 +125,6 @@
   </si>
   <si>
     <t>2025-04-13</t>
-  </si>
-  <si>
-    <t>2025-01-01</t>
   </si>
   <si>
     <t>2025-01-03</t>
@@ -263,7 +260,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -542,16 +539,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F40"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.15234375" customWidth="1"/>
-    <col min="3" max="3" width="15.69140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.3828125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.84375" customWidth="1"/>
-    <col min="6" max="6" width="59.3046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.140625" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
+    <col min="6" max="6" width="59.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -565,13 +562,13 @@
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>35</v>
       </c>
@@ -591,9 +588,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>18</v>
@@ -611,9 +608,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>19</v>
@@ -631,7 +628,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>34</v>
       </c>
@@ -651,9 +648,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>20</v>
@@ -671,9 +668,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>23</v>
@@ -691,9 +688,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>18</v>
@@ -711,9 +708,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>22</v>
@@ -731,9 +728,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>24</v>
@@ -751,9 +748,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>21</v>
@@ -771,9 +768,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>25</v>
@@ -791,9 +788,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>26</v>
@@ -811,9 +808,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>28</v>
@@ -831,9 +828,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>27</v>
@@ -851,9 +848,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>21</v>
@@ -871,9 +868,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>25</v>
@@ -891,9 +888,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>29</v>
@@ -911,9 +908,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>24</v>
@@ -931,9 +928,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>30</v>
@@ -951,9 +948,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>23</v>
@@ -971,9 +968,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>22</v>
@@ -991,9 +988,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>31</v>
@@ -1011,9 +1008,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>33</v>
@@ -1031,9 +1028,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>32</v>
@@ -1051,105 +1048,105 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
